--- a/entregables/revision_interna/COMPARACION_METRADO_EVACUACION_Y_SENALIZACION_HOGAR_REFUGIO.xlsx
+++ b/entregables/revision_interna/COMPARACION_METRADO_EVACUACION_Y_SENALIZACION_HOGAR_REFUGIO.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COMPARACIÓN'!$A$1:$I$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'POR EDIFICACIÓN'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'POR EDIFICACIÓN'!$A$1:$O$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'ERRORES DEL ARCHIVO'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>03.14.01.10</t>
@@ -1103,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G19" s="10">
         <f>F19-D19</f>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Conforme con el plano.</t>
+          <t>El hogar es solo para mujeres: las 20 señales de SS.HH. "mixto" del plano (19 en HD + la de la garita de control) son de SS.HH. mujeres. Total: 3 + 20 = 23.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G20" s="10">
         <f>F20-D20</f>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Falta la señal de la garita de control (SS.HH. del ingreso): son 20. Además, en HR sale 0 por un error de fórmula (ver hoja ERRORES DEL ARCHIVO).</t>
+          <t>No corresponde: el hogar es solo para mujeres. Las 20 señales "mixto" del plano (en HD 19; falta la de la garita) pasan a la partida de SS.HH. mujeres. Además, en HR sale 0 por un error de fórmula (HR!E26).</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="19" t="n"/>
       <c r="F27" s="19" t="n"/>
@@ -2419,13 +2419,21 @@
         <v>1</v>
       </c>
       <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
+      <c r="I27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>4</v>
+      </c>
       <c r="L27" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M27" s="19" t="n"/>
+      <c r="M27" s="19" t="n">
+        <v>1</v>
+      </c>
       <c r="N27" s="17">
         <f>SUM(D27:M27)</f>
         <v/>
@@ -2438,12 +2446,12 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>03.14.01.11</t>
+          <t>03.14.01.12</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>SUMINISTRO Y COLOCACION DE SEÑAL DE SS.HH MIXTOS</t>
+          <t>SUMINISTRO Y COLOCACION DE SEÑAL DE SS.HH DISCAPACITADOS</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -2456,17 +2464,15 @@
       </c>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="G28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="17">
@@ -2488,21 +2494,17 @@
       </c>
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>1</v>
+      </c>
       <c r="H29" s="19" t="n"/>
       <c r="I29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
       <c r="L29" s="19" t="n"/>
-      <c r="M29" s="19" t="n">
-        <v>1</v>
-      </c>
+      <c r="M29" s="19" t="n"/>
       <c r="N29" s="17">
         <f>SUM(D29:M29)</f>
         <v/>
@@ -2515,12 +2517,12 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>03.14.01.12</t>
+          <t>03.14.01.13</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>SUMINISTRO Y COLOCACION DE SEÑAL DE SS.HH DISCAPACITADOS</t>
+          <t>SUMINISTRO Y COLOCACION DE SEÑAL DE DETECTOR DE HUMO</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -2529,20 +2531,32 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="G30" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="17">
         <f>SUM(D30:M30)</f>
@@ -2559,21 +2573,35 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>5</v>
+      </c>
       <c r="G31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="19" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>12</v>
+      </c>
       <c r="I31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-      <c r="L31" s="19" t="n"/>
-      <c r="M31" s="19" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>1</v>
+      </c>
       <c r="N31" s="17">
         <f>SUM(D31:M31)</f>
         <v/>
@@ -2586,12 +2614,12 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>03.14.01.13</t>
+          <t>03.14.03.01</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>SUMINISTRO Y COLOCACION DE SEÑAL DE DETECTOR DE HUMO</t>
+          <t>EXTINTOR PQS 9 KG</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -2600,28 +2628,28 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>9</v>
-      </c>
       <c r="H32" s="8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L32" s="8" t="n">
         <v>1</v>
@@ -2642,136 +2670,39 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E33" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" s="19" t="n">
-        <v>9</v>
-      </c>
       <c r="H33" s="19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L33" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="19" t="n">
-        <v>1</v>
-      </c>
+      <c r="M33" s="19" t="n"/>
       <c r="N33" s="17">
         <f>SUM(D33:M33)</f>
         <v/>
       </c>
       <c r="O33" s="11">
         <f>IF(AND(D32=D33,E32=E33,F32=F33,G32=G33,H32=H33,I32=I33,J32=J33,K32=K33,L32=L33,M32=M33,N32=N33),"BIEN","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>03.14.03.01</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>EXTINTOR PQS 9 KG</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>HD arquitectura</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="17">
-        <f>SUM(D34:M34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr"/>
-      <c r="B35" s="12" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>Plano SE-S-02</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="K35" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="19" t="n"/>
-      <c r="N35" s="17">
-        <f>SUM(D35:M35)</f>
-        <v/>
-      </c>
-      <c r="O35" s="11">
-        <f>IF(AND(D34=D35,E34=E35,F34=F35,G34=G35,H34=H35,I34=I35,J34=J35,K34=K35,L34=L35,M34=M35,N34=N35),"BIEN","REVISAR")</f>
         <v/>
       </c>
     </row>
@@ -2785,7 +2716,7 @@
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="B5:O5"/>
   </mergeCells>
-  <conditionalFormatting sqref="O7:O36">
+  <conditionalFormatting sqref="O7:O34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BIEN"</formula>
     </cfRule>

--- a/entregables/revision_interna/COMPARACION_METRADO_EVACUACION_Y_SENALIZACION_HOGAR_REFUGIO.xlsx
+++ b/entregables/revision_interna/COMPARACION_METRADO_EVACUACION_Y_SENALIZACION_HOGAR_REFUGIO.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Total conforme con las 39 imágenes del plano (la leyenda dice 38). El reparto por edificación no se puede comprobar en el DXF (imágenes sin posición): se toma el de este metrado.</t>
+          <t>Conforme: las 39 imágenes del plano (la leyenda dice 38), ubicadas en el PDF de la lámina, dan el mismo reparto por edificación que este metrado.</t>
         </is>
       </c>
     </row>
